--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T11:03:45+00:00</t>
+    <t>2026-03-06T11:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T11:19:51+00:00</t>
+    <t>2026-03-11T07:45:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="308">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T07:45:24+00:00</t>
+    <t>2026-04-07T09:25:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -421,33 +421,53 @@
     <t>HealthcareService.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:cancellationPolicy</t>
+  </si>
+  <si>
+    <t>cancellationPolicy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+</t>
+  </si>
+  <si>
+    <t>The policy for a cancellation</t>
+  </si>
+  <si>
+    <t>This Extension provides the information about the policy of a cancellation of an appointment. It can contain a time frame until when a cancellation is possible or what the fee for a cancellation will be.</t>
+  </si>
+  <si>
+    <t>HealthcareService.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -455,6 +475,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -792,6 +815,9 @@
   </si>
   <si>
     <t>HealthcareService.eligibility.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1245,12 +1271,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.6796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.10546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.6796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.97265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1258,7 +1284,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="88.10546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.1875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2189,7 +2215,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2208,17 +2234,15 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>18</v>
@@ -2255,16 +2279,14 @@
         <v>18</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -2285,7 +2307,7 @@
         <v>18</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>18</v>
@@ -2296,43 +2318,41 @@
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>18</v>
       </c>
@@ -2380,7 +2400,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2398,7 +2418,7 @@
         <v>18</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>18</v>
@@ -2413,7 +2433,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2426,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>145</v>
@@ -2440,8 +2460,12 @@
       <c r="M11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>18</v>
       </c>
@@ -2489,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2501,16 +2525,16 @@
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -2529,13 +2553,13 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>85</v>
@@ -2549,16 +2573,12 @@
       <c r="M12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q12" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
         <v>18</v>
       </c>
@@ -2608,7 +2628,7 @@
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>18</v>
@@ -2617,21 +2637,21 @@
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2648,28 +2668,30 @@
         <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q13" s="2"/>
+      <c r="Q13" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="R13" t="s" s="2">
         <v>18</v>
       </c>
@@ -2713,7 +2735,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2728,21 +2750,21 @@
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>18</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2753,7 +2775,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>18</v>
@@ -2762,19 +2784,19 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2824,13 +2846,13 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
@@ -2842,7 +2864,7 @@
         <v>18</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>18</v>
@@ -2850,14 +2872,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2873,19 +2895,19 @@
         <v>18</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2911,13 +2933,13 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -2935,7 +2957,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2950,10 +2972,10 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>18</v>
@@ -2961,14 +2983,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2987,15 +3009,17 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3020,12 +3044,14 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y16" s="2"/>
-      <c r="Z16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
       </c>
@@ -3042,7 +3068,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3057,7 +3083,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>187</v>
@@ -3075,7 +3101,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3094,13 +3120,13 @@
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3127,11 +3153,9 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y17" t="s" s="2">
         <v>192</v>
       </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3169,7 +3193,7 @@
         <v>18</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>18</v>
@@ -3177,10 +3201,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3203,7 +3227,7 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>196</v>
@@ -3236,13 +3260,13 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -3260,7 +3284,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3275,10 +3299,10 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>18</v>
@@ -3286,10 +3310,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3300,7 +3324,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -3312,13 +3336,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3369,13 +3393,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
@@ -3384,21 +3408,21 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>205</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3421,17 +3445,15 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>210</v>
       </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -3480,7 +3502,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3501,15 +3523,15 @@
         <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>18</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3529,18 +3551,20 @@
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -3589,7 +3613,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3607,7 +3631,7 @@
         <v>18</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>18</v>
@@ -3615,10 +3639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3638,16 +3662,16 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3698,7 +3722,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3716,7 +3740,7 @@
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>18</v>
@@ -3724,10 +3748,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3738,7 +3762,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>18</v>
@@ -3747,23 +3771,19 @@
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O23" t="s" s="2">
         <v>226</v>
       </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
@@ -3811,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>18</v>
@@ -3829,7 +3849,7 @@
         <v>18</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>18</v>
@@ -3837,10 +3857,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3863,18 +3883,20 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
       </c>
@@ -3922,7 +3944,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3940,7 +3962,7 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>18</v>
@@ -3948,10 +3970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3974,16 +3996,16 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4009,31 +4031,31 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4051,7 +4073,7 @@
         <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>18</v>
@@ -4059,10 +4081,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4085,7 +4107,7 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>240</v>
@@ -4093,7 +4115,9 @@
       <c r="M26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N26" s="2"/>
+      <c r="N26" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4118,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
@@ -4142,7 +4166,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4160,7 +4184,7 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>18</v>
@@ -4168,10 +4192,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4182,7 +4206,7 @@
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -4194,13 +4218,13 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4257,19 +4281,19 @@
         <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>246</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>18</v>
@@ -4277,21 +4301,21 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4303,17 +4327,15 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -4362,25 +4384,25 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>18</v>
+        <v>253</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>18</v>
@@ -4388,14 +4410,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>252</v>
+        <v>144</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4408,26 +4430,24 @@
         <v>18</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -4475,7 +4495,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4493,7 +4513,7 @@
         <v>18</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>18</v>
@@ -4501,42 +4521,46 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -4560,10 +4584,10 @@
         <v>18</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>259</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>18</v>
@@ -4584,25 +4608,25 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>237</v>
+        <v>129</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>18</v>
@@ -4610,10 +4634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4636,17 +4660,15 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -4671,10 +4693,10 @@
         <v>18</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>18</v>
@@ -4695,7 +4717,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4713,7 +4735,7 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>18</v>
@@ -4721,10 +4743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4735,7 +4757,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -4747,16 +4769,16 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4782,13 +4804,13 @@
         <v>18</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>18</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>18</v>
@@ -4806,13 +4828,13 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>18</v>
@@ -4824,7 +4846,7 @@
         <v>18</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>18</v>
@@ -4832,10 +4854,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4858,16 +4880,16 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4893,13 +4915,13 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
@@ -4917,7 +4939,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4935,7 +4957,7 @@
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>18</v>
@@ -4943,10 +4965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4969,16 +4991,16 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5004,13 +5026,13 @@
         <v>18</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>109</v>
+        <v>284</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>110</v>
+        <v>285</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>18</v>
@@ -5028,7 +5050,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5046,7 +5068,7 @@
         <v>18</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>18</v>
+        <v>279</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>18</v>
@@ -5054,10 +5076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5080,15 +5102,17 @@
         <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
@@ -5113,31 +5137,31 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5155,7 +5179,7 @@
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>271</v>
+        <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>18</v>
@@ -5163,10 +5187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5177,7 +5201,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -5189,13 +5213,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5222,13 +5246,13 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>18</v>
+        <v>293</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>18</v>
+        <v>294</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -5246,13 +5270,13 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
@@ -5264,7 +5288,7 @@
         <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>18</v>
@@ -5272,10 +5296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5286,7 +5310,7 @@
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -5298,17 +5322,15 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>291</v>
+        <v>158</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -5357,13 +5379,13 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>18</v>
@@ -5375,7 +5397,7 @@
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>18</v>
@@ -5383,10 +5405,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5409,15 +5431,17 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -5466,7 +5490,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5484,9 +5508,118 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>18</v>
       </c>
     </row>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:25:26+00:00</t>
+    <t>2026-04-07T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:46:48+00:00</t>
+    <t>2026-06-09T10:31:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T10:31:34+00:00</t>
+    <t>2026-06-09T10:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-105-16---grafik-ergänzen/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T10:57:01+00:00</t>
+    <t>2026-06-09T12:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
